--- a/public/plantilla-cuentas.xlsx
+++ b/public/plantilla-cuentas.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuentas por Pagar" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,17 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -299,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,47 +330,47 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -407,17 +418,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -430,7 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -445,13 +456,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,10 +492,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,13 +513,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -518,7 +529,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -531,6 +542,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1040,9 +1087,9 @@
       </c>
       <c r="B10" s="90" t="n"/>
       <c r="C10" s="84" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="90" t="n"/>
-      <c r="F10" s="84" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="92" t="n"/>
+      <c r="F10" s="93" t="n"/>
       <c r="G10" s="22" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1050,10 +1097,10 @@
       </c>
       <c r="H10" s="90" t="n"/>
       <c r="I10" s="84" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="90" t="n"/>
-      <c r="L10" s="90" t="n"/>
-      <c r="M10" s="84" t="n"/>
+      <c r="J10" s="91" t="n"/>
+      <c r="K10" s="92" t="n"/>
+      <c r="L10" s="92" t="n"/>
+      <c r="M10" s="93" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="34">
       <c r="A11" s="22" t="inlineStr">
@@ -1063,9 +1110,9 @@
       </c>
       <c r="B11" s="90" t="n"/>
       <c r="C11" s="84" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="90" t="n"/>
-      <c r="F11" s="84" t="n"/>
+      <c r="D11" s="91" t="n"/>
+      <c r="E11" s="92" t="n"/>
+      <c r="F11" s="93" t="n"/>
       <c r="G11" s="22" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1073,10 +1120,10 @@
       </c>
       <c r="H11" s="90" t="n"/>
       <c r="I11" s="84" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="90" t="n"/>
-      <c r="L11" s="90" t="n"/>
-      <c r="M11" s="84" t="n"/>
+      <c r="J11" s="91" t="n"/>
+      <c r="K11" s="92" t="n"/>
+      <c r="L11" s="92" t="n"/>
+      <c r="M11" s="93" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="34">
       <c r="A12" s="22" t="inlineStr">
@@ -1086,9 +1133,9 @@
       </c>
       <c r="B12" s="90" t="n"/>
       <c r="C12" s="84" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="90" t="n"/>
-      <c r="F12" s="84" t="n"/>
+      <c r="D12" s="91" t="n"/>
+      <c r="E12" s="92" t="n"/>
+      <c r="F12" s="93" t="n"/>
       <c r="G12" s="22" t="inlineStr">
         <is>
           <t>Responsable del control</t>
@@ -1096,10 +1143,10 @@
       </c>
       <c r="H12" s="90" t="n"/>
       <c r="I12" s="84" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="90" t="n"/>
-      <c r="L12" s="90" t="n"/>
-      <c r="M12" s="84" t="n"/>
+      <c r="J12" s="91" t="n"/>
+      <c r="K12" s="92" t="n"/>
+      <c r="L12" s="92" t="n"/>
+      <c r="M12" s="93" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="34">
       <c r="A13" s="40" t="inlineStr">
@@ -1188,17 +1235,17 @@
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" s="34">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="24" t="n"/>
-      <c r="E15" s="88" t="n"/>
-      <c r="F15" s="88" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="8">
+      <c r="B15" s="91" t="n"/>
+      <c r="C15" s="91" t="n"/>
+      <c r="D15" s="91" t="n"/>
+      <c r="E15" s="95" t="n"/>
+      <c r="F15" s="95" t="n"/>
+      <c r="G15" s="96" t="n"/>
+      <c r="H15" s="96" t="n"/>
+      <c r="I15" s="97">
         <f>IF(G15="","",G15-N(H15))</f>
         <v/>
       </c>
@@ -1210,21 +1257,21 @@
         <f>IF(I15="","",IF(I15&lt;=0,"Pagada",IF(J15="","Pendiente",IF(J15&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="24" t="n"/>
+      <c r="L15" s="91" t="n"/>
+      <c r="M15" s="91" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="34">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="94" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="88" t="n"/>
-      <c r="F16" s="88" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="8">
+      <c r="B16" s="91" t="n"/>
+      <c r="C16" s="91" t="n"/>
+      <c r="D16" s="91" t="n"/>
+      <c r="E16" s="95" t="n"/>
+      <c r="F16" s="95" t="n"/>
+      <c r="G16" s="96" t="n"/>
+      <c r="H16" s="96" t="n"/>
+      <c r="I16" s="97">
         <f>IF(G16="","",G16-N(H16))</f>
         <v/>
       </c>
@@ -1236,21 +1283,21 @@
         <f>IF(I16="","",IF(I16&lt;=0,"Pagada",IF(J16="","Pendiente",IF(J16&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L16" s="24" t="n"/>
-      <c r="M16" s="24" t="n"/>
+      <c r="L16" s="91" t="n"/>
+      <c r="M16" s="91" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="34">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
-      <c r="E17" s="88" t="n"/>
-      <c r="F17" s="88" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="8">
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="95" t="n"/>
+      <c r="F17" s="95" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="97">
         <f>IF(G17="","",G17-N(H17))</f>
         <v/>
       </c>
@@ -1262,21 +1309,21 @@
         <f>IF(I17="","",IF(I17&lt;=0,"Pagada",IF(J17="","Pendiente",IF(J17&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L17" s="24" t="n"/>
-      <c r="M17" s="24" t="n"/>
+      <c r="L17" s="91" t="n"/>
+      <c r="M17" s="91" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="34">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="94" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="88" t="n"/>
-      <c r="F18" s="88" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="8">
+      <c r="B18" s="91" t="n"/>
+      <c r="C18" s="91" t="n"/>
+      <c r="D18" s="91" t="n"/>
+      <c r="E18" s="95" t="n"/>
+      <c r="F18" s="95" t="n"/>
+      <c r="G18" s="96" t="n"/>
+      <c r="H18" s="96" t="n"/>
+      <c r="I18" s="97">
         <f>IF(G18="","",G18-N(H18))</f>
         <v/>
       </c>
@@ -1288,21 +1335,21 @@
         <f>IF(I18="","",IF(I18&lt;=0,"Pagada",IF(J18="","Pendiente",IF(J18&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L18" s="24" t="n"/>
-      <c r="M18" s="24" t="n"/>
+      <c r="L18" s="91" t="n"/>
+      <c r="M18" s="91" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="34">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="88" t="n"/>
-      <c r="F19" s="88" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="8">
+      <c r="B19" s="91" t="n"/>
+      <c r="C19" s="91" t="n"/>
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="95" t="n"/>
+      <c r="F19" s="95" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="H19" s="96" t="n"/>
+      <c r="I19" s="97">
         <f>IF(G19="","",G19-N(H19))</f>
         <v/>
       </c>
@@ -1314,21 +1361,21 @@
         <f>IF(I19="","",IF(I19&lt;=0,"Pagada",IF(J19="","Pendiente",IF(J19&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L19" s="24" t="n"/>
-      <c r="M19" s="24" t="n"/>
+      <c r="L19" s="91" t="n"/>
+      <c r="M19" s="91" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="34">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="94" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="88" t="n"/>
-      <c r="F20" s="88" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="8">
+      <c r="B20" s="91" t="n"/>
+      <c r="C20" s="91" t="n"/>
+      <c r="D20" s="91" t="n"/>
+      <c r="E20" s="95" t="n"/>
+      <c r="F20" s="95" t="n"/>
+      <c r="G20" s="96" t="n"/>
+      <c r="H20" s="96" t="n"/>
+      <c r="I20" s="97">
         <f>IF(G20="","",G20-N(H20))</f>
         <v/>
       </c>
@@ -1340,21 +1387,21 @@
         <f>IF(I20="","",IF(I20&lt;=0,"Pagada",IF(J20="","Pendiente",IF(J20&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L20" s="24" t="n"/>
-      <c r="M20" s="24" t="n"/>
+      <c r="L20" s="91" t="n"/>
+      <c r="M20" s="91" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="34">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="24" t="n"/>
-      <c r="E21" s="88" t="n"/>
-      <c r="F21" s="88" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="8">
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="95" t="n"/>
+      <c r="F21" s="95" t="n"/>
+      <c r="G21" s="96" t="n"/>
+      <c r="H21" s="96" t="n"/>
+      <c r="I21" s="97">
         <f>IF(G21="","",G21-N(H21))</f>
         <v/>
       </c>
@@ -1366,21 +1413,21 @@
         <f>IF(I21="","",IF(I21&lt;=0,"Pagada",IF(J21="","Pendiente",IF(J21&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L21" s="24" t="n"/>
-      <c r="M21" s="24" t="n"/>
+      <c r="L21" s="91" t="n"/>
+      <c r="M21" s="91" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="34">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="94" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="88" t="n"/>
-      <c r="F22" s="88" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="8">
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="95" t="n"/>
+      <c r="F22" s="95" t="n"/>
+      <c r="G22" s="96" t="n"/>
+      <c r="H22" s="96" t="n"/>
+      <c r="I22" s="97">
         <f>IF(G22="","",G22-N(H22))</f>
         <v/>
       </c>
@@ -1392,21 +1439,21 @@
         <f>IF(I22="","",IF(I22&lt;=0,"Pagada",IF(J22="","Pendiente",IF(J22&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L22" s="24" t="n"/>
-      <c r="M22" s="24" t="n"/>
+      <c r="L22" s="91" t="n"/>
+      <c r="M22" s="91" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="34">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="94" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="88" t="n"/>
-      <c r="F23" s="88" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="8">
+      <c r="B23" s="91" t="n"/>
+      <c r="C23" s="91" t="n"/>
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="95" t="n"/>
+      <c r="F23" s="95" t="n"/>
+      <c r="G23" s="96" t="n"/>
+      <c r="H23" s="96" t="n"/>
+      <c r="I23" s="97">
         <f>IF(G23="","",G23-N(H23))</f>
         <v/>
       </c>
@@ -1418,21 +1465,21 @@
         <f>IF(I23="","",IF(I23&lt;=0,"Pagada",IF(J23="","Pendiente",IF(J23&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L23" s="24" t="n"/>
-      <c r="M23" s="24" t="n"/>
+      <c r="L23" s="91" t="n"/>
+      <c r="M23" s="91" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="34">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="94" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="88" t="n"/>
-      <c r="F24" s="88" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="8">
+      <c r="B24" s="91" t="n"/>
+      <c r="C24" s="91" t="n"/>
+      <c r="D24" s="91" t="n"/>
+      <c r="E24" s="95" t="n"/>
+      <c r="F24" s="95" t="n"/>
+      <c r="G24" s="96" t="n"/>
+      <c r="H24" s="96" t="n"/>
+      <c r="I24" s="97">
         <f>IF(G24="","",G24-N(H24))</f>
         <v/>
       </c>
@@ -1444,21 +1491,21 @@
         <f>IF(I24="","",IF(I24&lt;=0,"Pagada",IF(J24="","Pendiente",IF(J24&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L24" s="24" t="n"/>
-      <c r="M24" s="24" t="n"/>
+      <c r="L24" s="91" t="n"/>
+      <c r="M24" s="91" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="34">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="94" t="n">
         <v>11</v>
       </c>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="24" t="n"/>
-      <c r="E25" s="88" t="n"/>
-      <c r="F25" s="88" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="8">
+      <c r="B25" s="91" t="n"/>
+      <c r="C25" s="91" t="n"/>
+      <c r="D25" s="91" t="n"/>
+      <c r="E25" s="95" t="n"/>
+      <c r="F25" s="95" t="n"/>
+      <c r="G25" s="96" t="n"/>
+      <c r="H25" s="96" t="n"/>
+      <c r="I25" s="97">
         <f>IF(G25="","",G25-N(H25))</f>
         <v/>
       </c>
@@ -1470,21 +1517,21 @@
         <f>IF(I25="","",IF(I25&lt;=0,"Pagada",IF(J25="","Pendiente",IF(J25&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L25" s="24" t="n"/>
-      <c r="M25" s="24" t="n"/>
+      <c r="L25" s="91" t="n"/>
+      <c r="M25" s="91" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="34">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="94" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="88" t="n"/>
-      <c r="F26" s="88" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="8">
+      <c r="B26" s="91" t="n"/>
+      <c r="C26" s="91" t="n"/>
+      <c r="D26" s="91" t="n"/>
+      <c r="E26" s="95" t="n"/>
+      <c r="F26" s="95" t="n"/>
+      <c r="G26" s="96" t="n"/>
+      <c r="H26" s="96" t="n"/>
+      <c r="I26" s="97">
         <f>IF(G26="","",G26-N(H26))</f>
         <v/>
       </c>
@@ -1496,21 +1543,21 @@
         <f>IF(I26="","",IF(I26&lt;=0,"Pagada",IF(J26="","Pendiente",IF(J26&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L26" s="24" t="n"/>
-      <c r="M26" s="24" t="n"/>
+      <c r="L26" s="91" t="n"/>
+      <c r="M26" s="91" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="34">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="94" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="88" t="n"/>
-      <c r="F27" s="88" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="8">
+      <c r="B27" s="91" t="n"/>
+      <c r="C27" s="91" t="n"/>
+      <c r="D27" s="91" t="n"/>
+      <c r="E27" s="95" t="n"/>
+      <c r="F27" s="95" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="96" t="n"/>
+      <c r="I27" s="97">
         <f>IF(G27="","",G27-N(H27))</f>
         <v/>
       </c>
@@ -1522,21 +1569,21 @@
         <f>IF(I27="","",IF(I27&lt;=0,"Pagada",IF(J27="","Pendiente",IF(J27&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="24" t="n"/>
+      <c r="L27" s="91" t="n"/>
+      <c r="M27" s="91" t="n"/>
     </row>
     <row r="28" ht="22.05" customHeight="1" s="34">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="94" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="88" t="n"/>
-      <c r="F28" s="88" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="8">
+      <c r="B28" s="91" t="n"/>
+      <c r="C28" s="91" t="n"/>
+      <c r="D28" s="91" t="n"/>
+      <c r="E28" s="95" t="n"/>
+      <c r="F28" s="95" t="n"/>
+      <c r="G28" s="96" t="n"/>
+      <c r="H28" s="96" t="n"/>
+      <c r="I28" s="97">
         <f>IF(G28="","",G28-N(H28))</f>
         <v/>
       </c>
@@ -1548,21 +1595,21 @@
         <f>IF(I28="","",IF(I28&lt;=0,"Pagada",IF(J28="","Pendiente",IF(J28&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L28" s="24" t="n"/>
-      <c r="M28" s="24" t="n"/>
+      <c r="L28" s="91" t="n"/>
+      <c r="M28" s="91" t="n"/>
     </row>
     <row r="29" ht="22.05" customHeight="1" s="34">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="94" t="n">
         <v>15</v>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="88" t="n"/>
-      <c r="F29" s="88" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="8">
+      <c r="B29" s="91" t="n"/>
+      <c r="C29" s="91" t="n"/>
+      <c r="D29" s="91" t="n"/>
+      <c r="E29" s="95" t="n"/>
+      <c r="F29" s="95" t="n"/>
+      <c r="G29" s="96" t="n"/>
+      <c r="H29" s="96" t="n"/>
+      <c r="I29" s="97">
         <f>IF(G29="","",G29-N(H29))</f>
         <v/>
       </c>
@@ -1574,21 +1621,21 @@
         <f>IF(I29="","",IF(I29&lt;=0,"Pagada",IF(J29="","Pendiente",IF(J29&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L29" s="24" t="n"/>
-      <c r="M29" s="24" t="n"/>
+      <c r="L29" s="91" t="n"/>
+      <c r="M29" s="91" t="n"/>
     </row>
     <row r="30" ht="22.05" customHeight="1" s="34">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="94" t="n">
         <v>16</v>
       </c>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="88" t="n"/>
-      <c r="F30" s="88" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="8">
+      <c r="B30" s="91" t="n"/>
+      <c r="C30" s="91" t="n"/>
+      <c r="D30" s="91" t="n"/>
+      <c r="E30" s="95" t="n"/>
+      <c r="F30" s="95" t="n"/>
+      <c r="G30" s="96" t="n"/>
+      <c r="H30" s="96" t="n"/>
+      <c r="I30" s="97">
         <f>IF(G30="","",G30-N(H30))</f>
         <v/>
       </c>
@@ -1600,21 +1647,21 @@
         <f>IF(I30="","",IF(I30&lt;=0,"Pagada",IF(J30="","Pendiente",IF(J30&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L30" s="24" t="n"/>
-      <c r="M30" s="24" t="n"/>
+      <c r="L30" s="91" t="n"/>
+      <c r="M30" s="91" t="n"/>
     </row>
     <row r="31" ht="22.05" customHeight="1" s="34">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="94" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="88" t="n"/>
-      <c r="F31" s="88" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="8">
+      <c r="B31" s="91" t="n"/>
+      <c r="C31" s="91" t="n"/>
+      <c r="D31" s="91" t="n"/>
+      <c r="E31" s="95" t="n"/>
+      <c r="F31" s="95" t="n"/>
+      <c r="G31" s="96" t="n"/>
+      <c r="H31" s="96" t="n"/>
+      <c r="I31" s="97">
         <f>IF(G31="","",G31-N(H31))</f>
         <v/>
       </c>
@@ -1626,21 +1673,21 @@
         <f>IF(I31="","",IF(I31&lt;=0,"Pagada",IF(J31="","Pendiente",IF(J31&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L31" s="24" t="n"/>
-      <c r="M31" s="24" t="n"/>
+      <c r="L31" s="91" t="n"/>
+      <c r="M31" s="91" t="n"/>
     </row>
     <row r="32" ht="22.05" customHeight="1" s="34">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="94" t="n">
         <v>18</v>
       </c>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="88" t="n"/>
-      <c r="F32" s="88" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="8">
+      <c r="B32" s="91" t="n"/>
+      <c r="C32" s="91" t="n"/>
+      <c r="D32" s="91" t="n"/>
+      <c r="E32" s="95" t="n"/>
+      <c r="F32" s="95" t="n"/>
+      <c r="G32" s="96" t="n"/>
+      <c r="H32" s="96" t="n"/>
+      <c r="I32" s="97">
         <f>IF(G32="","",G32-N(H32))</f>
         <v/>
       </c>
@@ -1652,21 +1699,21 @@
         <f>IF(I32="","",IF(I32&lt;=0,"Pagada",IF(J32="","Pendiente",IF(J32&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L32" s="24" t="n"/>
-      <c r="M32" s="24" t="n"/>
+      <c r="L32" s="91" t="n"/>
+      <c r="M32" s="91" t="n"/>
     </row>
     <row r="33" ht="22.05" customHeight="1" s="34">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="94" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="24" t="n"/>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="24" t="n"/>
-      <c r="E33" s="88" t="n"/>
-      <c r="F33" s="88" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="8">
+      <c r="B33" s="91" t="n"/>
+      <c r="C33" s="91" t="n"/>
+      <c r="D33" s="91" t="n"/>
+      <c r="E33" s="95" t="n"/>
+      <c r="F33" s="95" t="n"/>
+      <c r="G33" s="96" t="n"/>
+      <c r="H33" s="96" t="n"/>
+      <c r="I33" s="97">
         <f>IF(G33="","",G33-N(H33))</f>
         <v/>
       </c>
@@ -1678,21 +1725,21 @@
         <f>IF(I33="","",IF(I33&lt;=0,"Pagada",IF(J33="","Pendiente",IF(J33&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L33" s="24" t="n"/>
-      <c r="M33" s="24" t="n"/>
+      <c r="L33" s="91" t="n"/>
+      <c r="M33" s="91" t="n"/>
     </row>
     <row r="34" ht="22.05" customHeight="1" s="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="94" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="88" t="n"/>
-      <c r="F34" s="88" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="8">
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="91" t="n"/>
+      <c r="D34" s="91" t="n"/>
+      <c r="E34" s="95" t="n"/>
+      <c r="F34" s="95" t="n"/>
+      <c r="G34" s="96" t="n"/>
+      <c r="H34" s="96" t="n"/>
+      <c r="I34" s="97">
         <f>IF(G34="","",G34-N(H34))</f>
         <v/>
       </c>
@@ -1704,8 +1751,8 @@
         <f>IF(I34="","",IF(I34&lt;=0,"Pagada",IF(J34="","Pendiente",IF(J34&gt;0,"Vencida","Por vencer"))))</f>
         <v/>
       </c>
-      <c r="L34" s="24" t="n"/>
-      <c r="M34" s="24" t="n"/>
+      <c r="L34" s="91" t="n"/>
+      <c r="M34" s="91" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="36" t="inlineStr">
@@ -1718,15 +1765,15 @@
       <c r="D35" s="90" t="n"/>
       <c r="E35" s="90" t="n"/>
       <c r="F35" s="84" t="n"/>
-      <c r="G35" s="86">
+      <c r="G35" s="98">
         <f>SUM(G15:G34)</f>
         <v/>
       </c>
-      <c r="H35" s="86">
+      <c r="H35" s="98">
         <f>SUM(H15:H34)</f>
         <v/>
       </c>
-      <c r="I35" s="86">
+      <c r="I35" s="98">
         <f>SUM(I15:I34)</f>
         <v/>
       </c>
@@ -1755,7 +1802,7 @@
       <c r="L37" s="90" t="n"/>
       <c r="M37" s="84" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="55" customHeight="1" s="34">
       <c r="B38" s="31" t="inlineStr">
         <is>
           <t>Rango</t>
@@ -1772,7 +1819,7 @@
           <t>% del saldo</t>
         </is>
       </c>
-      <c r="G38" s="24" t="inlineStr">
+      <c r="G38" s="94" t="inlineStr">
         <is>
           <t>Los días de mora se cuentan desde la fecha de vencimiento hasta la fecha de corte.
 «Por vencer» es una deuda cuya fecha de vencimiento aún no llega.
@@ -1787,18 +1834,18 @@
       <c r="M38" s="48" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="n"/>
+      <c r="A39" s="91" t="n"/>
       <c r="B39" s="22" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
       </c>
       <c r="C39" s="84" t="n"/>
-      <c r="D39" s="41">
+      <c r="D39" s="99">
         <f>SUMIF($K$15:$K$34,"Por vencer",$I$15:$I$34)</f>
         <v/>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="100">
         <f>IF($I$35=0,"",D39/$I$35)</f>
         <v/>
       </c>
@@ -1806,18 +1853,18 @@
       <c r="M39" s="50" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
+      <c r="A40" s="91" t="n"/>
       <c r="B40" s="22" t="inlineStr">
         <is>
           <t>Vencida de 1 a 30 días</t>
         </is>
       </c>
       <c r="C40" s="84" t="n"/>
-      <c r="D40" s="41">
+      <c r="D40" s="99">
         <f>SUMIFS($I$15:$I$34,$K$15:$K$34,"Vencida",$J$15:$J$34,"&gt;=1",$J$15:$J$34,"&lt;=30")</f>
         <v/>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="100">
         <f>IF($I$35=0,"",D40/$I$35)</f>
         <v/>
       </c>
@@ -1825,18 +1872,18 @@
       <c r="M40" s="50" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="n"/>
+      <c r="A41" s="91" t="n"/>
       <c r="B41" s="22" t="inlineStr">
         <is>
           <t>Vencida de 31 a 60 días</t>
         </is>
       </c>
       <c r="C41" s="84" t="n"/>
-      <c r="D41" s="41">
+      <c r="D41" s="99">
         <f>SUMIFS($I$15:$I$34,$K$15:$K$34,"Vencida",$J$15:$J$34,"&gt;=31",$J$15:$J$34,"&lt;=60")</f>
         <v/>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="100">
         <f>IF($I$35=0,"",D41/$I$35)</f>
         <v/>
       </c>
@@ -1844,18 +1891,18 @@
       <c r="M41" s="50" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="n"/>
+      <c r="A42" s="91" t="n"/>
       <c r="B42" s="22" t="inlineStr">
         <is>
           <t>Vencida de 61 a 90 días</t>
         </is>
       </c>
       <c r="C42" s="84" t="n"/>
-      <c r="D42" s="41">
+      <c r="D42" s="99">
         <f>SUMIFS($I$15:$I$34,$K$15:$K$34,"Vencida",$J$15:$J$34,"&gt;=61",$J$15:$J$34,"&lt;=90")</f>
         <v/>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="100">
         <f>IF($I$35=0,"",D42/$I$35)</f>
         <v/>
       </c>
@@ -1863,18 +1910,18 @@
       <c r="M42" s="50" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="n"/>
+      <c r="A43" s="91" t="n"/>
       <c r="B43" s="22" t="inlineStr">
         <is>
           <t>Vencida de más de 90 días</t>
         </is>
       </c>
       <c r="C43" s="84" t="n"/>
-      <c r="D43" s="41">
+      <c r="D43" s="99">
         <f>SUMIFS($I$15:$I$34,$K$15:$K$34,"Vencida",$J$15:$J$34,"&gt;90")</f>
         <v/>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="100">
         <f>IF($I$35=0,"",D43/$I$35)</f>
         <v/>
       </c>
@@ -1882,18 +1929,18 @@
       <c r="M43" s="50" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="n"/>
+      <c r="A44" s="91" t="n"/>
       <c r="B44" s="22" t="inlineStr">
         <is>
           <t>Pendiente sin fecha de corte o de vencimiento</t>
         </is>
       </c>
       <c r="C44" s="84" t="n"/>
-      <c r="D44" s="41">
+      <c r="D44" s="99">
         <f>SUMIF($K$15:$K$34,"Pendiente",$I$15:$I$34)</f>
         <v/>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="100">
         <f>IF($I$35=0,"",D44/$I$35)</f>
         <v/>
       </c>
@@ -1908,11 +1955,11 @@
       </c>
       <c r="B45" s="90" t="n"/>
       <c r="C45" s="84" t="n"/>
-      <c r="D45" s="86">
+      <c r="D45" s="98">
         <f>SUM(D39:D44)</f>
         <v/>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="101">
         <f>IF(D45=0,"",1)</f>
         <v/>
       </c>
@@ -1975,9 +2022,9 @@
       </c>
       <c r="B49" s="90" t="n"/>
       <c r="C49" s="84" t="n"/>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="90" t="n"/>
-      <c r="F49" s="84" t="n"/>
+      <c r="D49" s="91" t="n"/>
+      <c r="E49" s="92" t="n"/>
+      <c r="F49" s="93" t="n"/>
       <c r="G49" s="22" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1985,10 +2032,10 @@
       </c>
       <c r="H49" s="90" t="n"/>
       <c r="I49" s="84" t="n"/>
-      <c r="J49" s="24" t="n"/>
-      <c r="K49" s="90" t="n"/>
-      <c r="L49" s="90" t="n"/>
-      <c r="M49" s="84" t="n"/>
+      <c r="J49" s="91" t="n"/>
+      <c r="K49" s="92" t="n"/>
+      <c r="L49" s="92" t="n"/>
+      <c r="M49" s="93" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="34">
       <c r="A50" s="22" t="inlineStr">
@@ -1998,9 +2045,9 @@
       </c>
       <c r="B50" s="90" t="n"/>
       <c r="C50" s="84" t="n"/>
-      <c r="D50" s="24" t="n"/>
-      <c r="E50" s="90" t="n"/>
-      <c r="F50" s="84" t="n"/>
+      <c r="D50" s="91" t="n"/>
+      <c r="E50" s="92" t="n"/>
+      <c r="F50" s="93" t="n"/>
       <c r="G50" s="22" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -2008,10 +2055,10 @@
       </c>
       <c r="H50" s="90" t="n"/>
       <c r="I50" s="84" t="n"/>
-      <c r="J50" s="24" t="n"/>
-      <c r="K50" s="90" t="n"/>
-      <c r="L50" s="90" t="n"/>
-      <c r="M50" s="84" t="n"/>
+      <c r="J50" s="91" t="n"/>
+      <c r="K50" s="92" t="n"/>
+      <c r="L50" s="92" t="n"/>
+      <c r="M50" s="93" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="34">
       <c r="A51" s="22" t="inlineStr">
@@ -2021,9 +2068,9 @@
       </c>
       <c r="B51" s="90" t="n"/>
       <c r="C51" s="84" t="n"/>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="90" t="n"/>
-      <c r="F51" s="84" t="n"/>
+      <c r="D51" s="91" t="n"/>
+      <c r="E51" s="92" t="n"/>
+      <c r="F51" s="93" t="n"/>
       <c r="G51" s="22" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -2031,12 +2078,13 @@
       </c>
       <c r="H51" s="90" t="n"/>
       <c r="I51" s="84" t="n"/>
-      <c r="J51" s="24" t="n"/>
-      <c r="K51" s="90" t="n"/>
-      <c r="L51" s="90" t="n"/>
-      <c r="M51" s="84" t="n"/>
+      <c r="J51" s="91" t="n"/>
+      <c r="K51" s="92" t="n"/>
+      <c r="L51" s="92" t="n"/>
+      <c r="M51" s="93" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="54">
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="D11:F11"/>
